--- a/docs/培训/OpenWorker培训/04-备件盘点/出入库记录.xlsx
+++ b/docs/培训/OpenWorker培训/04-备件盘点/出入库记录.xlsx
@@ -482,7 +482,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46238</v>
+        <v>46244</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -520,7 +520,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46238</v>
+        <v>46244</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -558,7 +558,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46238</v>
+        <v>46244</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46238</v>
+        <v>46244</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -634,7 +634,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46238</v>
+        <v>46244</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -672,7 +672,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46238</v>
+        <v>46244</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46238</v>
+        <v>46244</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46238</v>
+        <v>46244</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46238</v>
+        <v>46244</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46239</v>
+        <v>46245</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46239</v>
+        <v>46245</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46239</v>
+        <v>46245</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46239</v>
+        <v>46245</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46244</v>
+        <v>46248</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46245</v>
+        <v>46251</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46246</v>
+        <v>46252</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46246</v>
+        <v>46252</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46247</v>
+        <v>46253</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46247</v>
+        <v>46253</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46247</v>
+        <v>46253</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>46247</v>
+        <v>46253</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>46247</v>
+        <v>46253</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>46248</v>
+        <v>46254</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>46252</v>
+        <v>46258</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>46254</v>
+        <v>46260</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>46254</v>
+        <v>46260</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>46254</v>
+        <v>46260</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>46255</v>
+        <v>46261</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1546,7 +1546,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>46255</v>
+        <v>46261</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>46258</v>
+        <v>46262</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>46258</v>
+        <v>46262</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>46258</v>
+        <v>46262</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>46258</v>
+        <v>46262</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>46258</v>
+        <v>46262</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>46259</v>
+        <v>46265</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>46261</v>
+        <v>46267</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>46261</v>
+        <v>46267</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>46261</v>
+        <v>46267</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>46266</v>
+        <v>46272</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>46267</v>
+        <v>46273</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>46268</v>
+        <v>46274</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>46268</v>
+        <v>46274</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>46268</v>
+        <v>46274</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>46268</v>
+        <v>46274</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>46268</v>
+        <v>46274</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>46269</v>
+        <v>46275</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>46269</v>
+        <v>46275</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>46273</v>
+        <v>46279</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>46273</v>
+        <v>46279</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>46273</v>
+        <v>46279</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>46273</v>
+        <v>46279</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>46273</v>
+        <v>46279</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>46273</v>
+        <v>46279</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>46279</v>
+        <v>46283</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>46279</v>
+        <v>46283</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>46279</v>
+        <v>46283</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>46279</v>
+        <v>46283</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>46279</v>
+        <v>46283</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>46279</v>
+        <v>46283</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>46279</v>
+        <v>46283</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>46279</v>
+        <v>46283</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>46280</v>
+        <v>46286</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>46280</v>
+        <v>46286</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>46280</v>
+        <v>46286</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>46280</v>
+        <v>46286</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>46280</v>
+        <v>46286</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>46280</v>
+        <v>46286</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>46282</v>
+        <v>46288</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>46286</v>
+        <v>46290</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>46286</v>
+        <v>46290</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>46286</v>
+        <v>46290</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>46286</v>
+        <v>46290</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -3218,7 +3218,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>46288</v>
+        <v>46294</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>46290</v>
+        <v>46296</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>46293</v>
+        <v>46297</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>46293</v>
+        <v>46297</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>46293</v>
+        <v>46297</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>46293</v>
+        <v>46297</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>46293</v>
+        <v>46297</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>46293</v>
+        <v>46297</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
